--- a/data publikasi new.xlsx
+++ b/data publikasi new.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\APLIKASI PYTHON STREAMLIT 2026\DATA PRODI S1 MATEMATIKA USU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C4F7CD-FA2C-49F8-B6D4-85BEE0CC149D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3742BC8-E4A2-4BA3-81C1-42783B3311E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="189">
   <si>
     <t>Judul</t>
   </si>
@@ -382,6 +382,216 @@
   </si>
   <si>
     <t>10.1063/5.0128452</t>
+  </si>
+  <si>
+    <t>Multi-Criteria decision making model for CSR program planning in the direction of a sustainable CPO industry</t>
+  </si>
+  <si>
+    <t>Tua Halomoan Harahap; Herman Mawengkang; Saib Suwilo; Sutarman</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85160255510?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://pubs.aip.org/aip/acp/article-abstract/2714/1/030045/2889778/Multi-Criteria-decision-making-model-for-CSR?redirectedFrom=fulltext</t>
+  </si>
+  <si>
+    <t>10.1063/5.0128455</t>
+  </si>
+  <si>
+    <t>Logistics distribution supply chain optimization model with VRP in the context of E-commerce</t>
+  </si>
+  <si>
+    <t>M. Khahfi Zuhanda; Herman Mawengkang; Saib Suwilo; Mardiningsih; Opim Salim Sitompul</t>
+  </si>
+  <si>
+    <t>Herman Mawengkang; Saib Suwilo; Mardiningsih; Opim Salim Sitompul</t>
+  </si>
+  <si>
+    <t>https://pubs.aip.org/aip/acp/article-abstract/2714/1/020049/2889719/Logistics-distribution-supply-chain-optimization?redirectedFrom=fulltext</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85160248125?origin=resultslist</t>
+  </si>
+  <si>
+    <t>10.1063/5.0128465</t>
+  </si>
+  <si>
+    <t>A mixed-integer model for aircraft fleet assignment and manpower planning problems under uncertainty</t>
+  </si>
+  <si>
+    <t>Rianita Simamora; Herman Mawengkang;  Saib Suwilo; Muhammad Zarlis</t>
+  </si>
+  <si>
+    <t>Herman Mawengkang;  Saib Suwilo; Muhammad Zarlis</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85160245302?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://pubs.aip.org/aip/acp/article-abstract/2714/1/030042/2889728/A-mixed-integer-model-for-aircraft-fleet?redirectedFrom=fulltext</t>
+  </si>
+  <si>
+    <t>10.1063/5.0128467</t>
+  </si>
+  <si>
+    <t>Development of heuristic method for scenario formation of stochastic program problems</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85160233635?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://pubs.aip.org/aip/acp/article-abstract/2714/1/030053/2889792/Development-of-heuristic-method-for-scenario?redirectedFrom=fulltext</t>
+  </si>
+  <si>
+    <t>10.1063/5.0128477</t>
+  </si>
+  <si>
+    <t>Multi-objective optimization model supply chain network design by considering supply uncertainty</t>
+  </si>
+  <si>
+    <t>Puteri Fajar Addini; Saib Suwilo; Herman Mawengkang</t>
+  </si>
+  <si>
+    <t>Saib Suwilo; Herman Mawengkang</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85160217465?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://pubs.aip.org/aip/acp/article-abstract/2714/1/020054/2889722/Multi-objective-optimization-model-supply-chain?redirectedFrom=fulltext</t>
+  </si>
+  <si>
+    <t>10.1063/5.0128479</t>
+  </si>
+  <si>
+    <t>On solving robust optimization using decomposition approach</t>
+  </si>
+  <si>
+    <t>Hendra Cipta; Saib Suwilo; Sutarman; Herman Mawengkang</t>
+  </si>
+  <si>
+    <t>Saib Suwilo; Sutarman; Herman Mawengkang</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85160216337?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://pubs.aip.org/aip/acp/article-abstract/2714/1/030039/2889786/On-solving-robust-optimization-using-decomposition?redirectedFrom=fulltext</t>
+  </si>
+  <si>
+    <t>10.1063/5.0128480</t>
+  </si>
+  <si>
+    <t>Signcryption Techniques For Digital File Security Using the RSA Multi-Factor Algorithm and the ESIGN Algorithm</t>
+  </si>
+  <si>
+    <t>Taupan Syah Putra; Mohammad Andri Budiman; Saib Suwilo</t>
+  </si>
+  <si>
+    <t>Mohammad Andri Budiman; Saib Suwilo</t>
+  </si>
+  <si>
+    <t>2023 IEEE International Conference of Computer Science and Information Technology: The Role of Artificial Intelligence Technology in Human and Computer Interactions in the Industrial Era 5.0, ICOSNIKOM 2023</t>
+  </si>
+  <si>
+    <t>979-8-3503-6075-2</t>
+  </si>
+  <si>
+    <t>10.1109/ICoSNIKOM60230.2023.10364520</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85182941246?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/document/10364520</t>
+  </si>
+  <si>
+    <t>Generalized Lambda Distribution: Application on Financial Performance Data in the Indonesia Stock Exchange</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85182928287?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/document/10364340</t>
+  </si>
+  <si>
+    <t>Analysis and Improvement of JPEG Compression Performance with Discrete Cosine Transform and Convolution Gaussian Filtering</t>
+  </si>
+  <si>
+    <t>Ronald Suryadi Purba; Tulus; Saib Suwilo</t>
+  </si>
+  <si>
+    <t>Tulus; Saib Suwilo</t>
+  </si>
+  <si>
+    <t>Proceedings - 2023 IEEE International Conference on Cryptography, Informatics, and Cybersecurity: Cryptography and Cybersecurity: Roles, Prospects, and Challenges, ICoCICs 2023</t>
+  </si>
+  <si>
+    <t>979-8-3503-3943-7</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85175447401?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/document/10277096</t>
+  </si>
+  <si>
+    <t>10.1109/ICoCICs58778.2023.10277096</t>
+  </si>
+  <si>
+    <t>Community Clustering on Fraud Transactions Applied the Louvain-Coloring Algorithm</t>
+  </si>
+  <si>
+    <t>Heru Mardiansyah; Saib Suwilo; Erna Budiarti Nababan; Syahril Efendi</t>
+  </si>
+  <si>
+    <t>Saib Suwilo; Erna Budiarti Nababan; Syahril Efendi</t>
+  </si>
+  <si>
+    <t>International Journal of Electronics and Telecommunications</t>
+  </si>
+  <si>
+    <t>593-598</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85169425156?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://journals.pan.pl/dlibra/publication/146512/edition/128301/content</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=20000195009&amp;tip=sid&amp;clean=0</t>
+  </si>
+  <si>
+    <t>10.24425/ijet.2023.146512</t>
+  </si>
+  <si>
+    <t>Muhammad Khahfi Zuhanda; Saib Suwilo; Opim Salim Sitompul; Mardiningsih; Rezzy Eko Caraka; Yunho Kim; Maengseok Noh</t>
+  </si>
+  <si>
+    <t>Optimization of Vehicle Routing Problem in the Context of E-commerce Logistics Distribution</t>
+  </si>
+  <si>
+    <t>Saib Suwilo; Opim Salim Sitompul; Mardiningsih; Rezzy Eko Caraka; Yunho Kim; Maengseok Noh</t>
+  </si>
+  <si>
+    <t>Engineering Letters</t>
+  </si>
+  <si>
+    <t>1816093X</t>
+  </si>
+  <si>
+    <t>1-8</t>
+  </si>
+  <si>
+    <t>https://www.scopus.com/pages/publications/85151963574?origin=resultslist</t>
+  </si>
+  <si>
+    <t>https://www.engineeringletters.com/issues_v31/issue_1/EL_31_1_29.pdf</t>
+  </si>
+  <si>
+    <t>https://www.scimagojr.com/journalsearch.php?q=17800156701&amp;tip=sid&amp;clean=0</t>
   </si>
 </sst>
 </file>
@@ -718,7 +928,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="67.5703125" style="1" customWidth="1"/>
@@ -1342,6 +1552,481 @@
         <v>118</v>
       </c>
       <c r="R13" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G14" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H14" s="1">
+        <v>2714</v>
+      </c>
+      <c r="I14" s="1">
+        <v>1</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G15" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H15" s="1">
+        <v>2714</v>
+      </c>
+      <c r="I15" s="1">
+        <v>1</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="P15" s="1">
+        <v>7</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G16" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H16" s="1">
+        <v>2714</v>
+      </c>
+      <c r="I16" s="1">
+        <v>1</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G17" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H17" s="1">
+        <v>2714</v>
+      </c>
+      <c r="I17" s="1">
+        <v>1</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G18" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H18" s="1">
+        <v>2714</v>
+      </c>
+      <c r="I18" s="1">
+        <v>1</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G19" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H19" s="1">
+        <v>2714</v>
+      </c>
+      <c r="I19" s="1">
+        <v>1</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G20" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="P20" s="1">
+        <v>1</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G21" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G22" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="P22" s="1">
+        <v>3</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="F23" s="1">
+        <v>20818491</v>
+      </c>
+      <c r="G23" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H23" s="1">
+        <v>69</v>
+      </c>
+      <c r="I23" s="1">
+        <v>3</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="P23" s="1">
+        <v>1</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G24" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H24" s="1">
+        <v>31</v>
+      </c>
+      <c r="I24" s="1">
+        <v>1</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="P24" s="1">
+        <v>7</v>
+      </c>
+      <c r="R24" s="1" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1385,6 +2070,36 @@
     <hyperlink ref="L13" r:id="rId36" xr:uid="{8498E7FC-CE4E-49F5-AB27-77371EC4B557}"/>
     <hyperlink ref="K13" r:id="rId37" xr:uid="{B12A011E-C640-4608-8DCD-BC0B115F50EC}"/>
     <hyperlink ref="N13" r:id="rId38" xr:uid="{586704EE-283F-49B1-AF27-B3B67CD6E231}"/>
+    <hyperlink ref="K14" r:id="rId39" xr:uid="{E1BEA553-8F37-44BB-B2A8-06BBC1F608F3}"/>
+    <hyperlink ref="L14" r:id="rId40" xr:uid="{117E2551-331F-40FD-A936-5777840A8720}"/>
+    <hyperlink ref="N14" r:id="rId41" xr:uid="{9F0CD2C2-4E8A-4C33-BE7E-1264DEF9D4C4}"/>
+    <hyperlink ref="L15" r:id="rId42" xr:uid="{143D0A8A-8952-4169-AF11-F292ED435311}"/>
+    <hyperlink ref="K15" r:id="rId43" xr:uid="{C55E5DFE-9918-4666-BD60-DB7564DDE4CC}"/>
+    <hyperlink ref="N15" r:id="rId44" xr:uid="{027BB151-C42A-4377-8CC4-3E6AEB9E37F8}"/>
+    <hyperlink ref="K16" r:id="rId45" xr:uid="{603A0E48-52F8-4E06-800B-3DCD3F5A8FA2}"/>
+    <hyperlink ref="L16" r:id="rId46" xr:uid="{2E461DEB-83F3-4162-AD55-8E50B7C78134}"/>
+    <hyperlink ref="N16" r:id="rId47" xr:uid="{DEE621B6-4566-4F9E-AFB7-AEDBFAE8C3A9}"/>
+    <hyperlink ref="K17" r:id="rId48" xr:uid="{7C2F6C92-6704-4895-AB6F-48C12A7A92B4}"/>
+    <hyperlink ref="L17" r:id="rId49" xr:uid="{290ABAF0-EC44-4BD7-B12A-26EC30044F32}"/>
+    <hyperlink ref="N17" r:id="rId50" xr:uid="{45CB862C-8327-4F80-9F97-6D39FA1AABF6}"/>
+    <hyperlink ref="K18" r:id="rId51" xr:uid="{4833A04C-C34A-4296-8836-88C47C87BB85}"/>
+    <hyperlink ref="L18" r:id="rId52" xr:uid="{BCD74009-20D7-40E8-9856-03077E3EFCB9}"/>
+    <hyperlink ref="N18" r:id="rId53" xr:uid="{B2E8382F-21F2-4462-B169-1EEBCF98A9F3}"/>
+    <hyperlink ref="K19" r:id="rId54" xr:uid="{932125B5-24D6-4E12-9A7E-E249D5C03C73}"/>
+    <hyperlink ref="L19" r:id="rId55" xr:uid="{0FEB77E1-F00F-4932-BC70-659841EED1AE}"/>
+    <hyperlink ref="N19" r:id="rId56" xr:uid="{46584C22-384F-48BC-B30A-3E97A79605E2}"/>
+    <hyperlink ref="K20" r:id="rId57" xr:uid="{F8A589CB-F2CA-493A-9425-284426EA342C}"/>
+    <hyperlink ref="L20" r:id="rId58" xr:uid="{85326ABC-B52A-4C18-BCC4-572873A64F5E}"/>
+    <hyperlink ref="K21" r:id="rId59" xr:uid="{164A44B9-A38C-4376-9317-6DBC5BB6837D}"/>
+    <hyperlink ref="L21" r:id="rId60" xr:uid="{6D658E0C-5FDB-4EED-83E2-66D05483ED95}"/>
+    <hyperlink ref="K22" r:id="rId61" xr:uid="{648B1075-EDFC-46D0-9EA4-2661EB10E5C4}"/>
+    <hyperlink ref="L22" r:id="rId62" xr:uid="{36DA944B-1B79-481A-9806-5846A0F88008}"/>
+    <hyperlink ref="K23" r:id="rId63" xr:uid="{3011F02A-5DC4-4138-943C-7E6DDEF2CDE3}"/>
+    <hyperlink ref="L23" r:id="rId64" xr:uid="{5FA09C68-CDAD-49CF-A606-D1E36AE31EA9}"/>
+    <hyperlink ref="N23" r:id="rId65" xr:uid="{CFE7BBC7-A974-4D01-828E-47B6B3C9A4AC}"/>
+    <hyperlink ref="K24" r:id="rId66" xr:uid="{C8103ED1-58D5-4F01-86A4-DBB09809EB95}"/>
+    <hyperlink ref="L24" r:id="rId67" xr:uid="{F0FE5802-FBA3-433C-8703-069A67E18980}"/>
+    <hyperlink ref="N24" r:id="rId68" xr:uid="{768774F2-C6D1-4D60-892B-38D23C0306AC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
